--- a/forms/app/quality_monitoring_follow_up.xlsx
+++ b/forms/app/quality_monitoring_follow_up.xlsx
@@ -10,15 +10,15 @@
   <definedNames/>
   <calcPr/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataSignature="AMtx7mgJbxkpRJ660NKkHotuOcLnSHvZeA=="/>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="dkctA4Pdn0z9hP41QPlhhvEXkZvyM3Uz9mKgzhFMhow="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="116">
   <si>
     <t>type</t>
   </si>
@@ -50,10 +50,10 @@
     <t>constraint_message::sw</t>
   </si>
   <si>
-    <t>calculation</t>
+    <t>repeat_count</t>
   </si>
   <si>
-    <t>repeat_count</t>
+    <t>calculation</t>
   </si>
   <si>
     <t>default</t>
@@ -215,6 +215,15 @@
     <t>selected(${follow_up_again}, "yes")</t>
   </si>
   <si>
+    <t>. &gt; today()</t>
+  </si>
+  <si>
+    <t>Date cannot be a past date or today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tafadhali chagua tarehe ya mbele </t>
+  </si>
+  <si>
     <t>group_summary</t>
   </si>
   <si>
@@ -368,7 +377,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dmmyyyyhm"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -386,13 +395,28 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans&quot;"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -401,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -411,8 +435,11 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
@@ -643,7 +670,9 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="18.0"/>
     <col customWidth="1" min="2" max="2" width="18.5"/>
-    <col customWidth="1" min="3" max="26" width="18.0"/>
+    <col customWidth="1" min="3" max="9" width="18.0"/>
+    <col customWidth="1" min="10" max="10" width="17.63"/>
+    <col customWidth="1" min="11" max="26" width="18.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -745,7 +774,7 @@
       <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="2"/>
@@ -779,7 +808,7 @@
       <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="2"/>
@@ -813,7 +842,7 @@
       <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="2"/>
@@ -925,10 +954,10 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="2"/>
+      <c r="L8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -961,10 +990,10 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -987,7 +1016,7 @@
       <c r="B10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="2"/>
@@ -1197,10 +1226,10 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="2"/>
+      <c r="L16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -1231,10 +1260,10 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
-      <c r="K17" s="2" t="s">
+      <c r="K17" s="2"/>
+      <c r="L17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -1265,10 +1294,10 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="2"/>
+      <c r="L18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -1299,10 +1328,10 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
-      <c r="K19" s="2" t="s">
+      <c r="K19" s="2"/>
+      <c r="L19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -1571,9 +1600,15 @@
         <v>64</v>
       </c>
       <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
+      <c r="H27" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -1656,259 +1691,259 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+        <v>69</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
       <c r="G30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="4"/>
-      <c r="Z30" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="5"/>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5"/>
+      <c r="Z30" s="5"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
+        <v>74</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
       <c r="G31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
-      <c r="Z31" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5"/>
+      <c r="Z31" s="5"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
-      <c r="W32" s="4"/>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="4"/>
-      <c r="Z32" s="4"/>
+        <v>78</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+      <c r="W32" s="5"/>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="5"/>
+      <c r="Z32" s="5"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
+        <v>81</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
       <c r="G33" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="4"/>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="4"/>
-      <c r="Z33" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="5"/>
+      <c r="X33" s="5"/>
+      <c r="Y33" s="5"/>
+      <c r="Z33" s="5"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="4"/>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4"/>
-      <c r="Y34" s="4"/>
-      <c r="Z34" s="4"/>
+        <v>84</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+      <c r="W34" s="5"/>
+      <c r="X34" s="5"/>
+      <c r="Y34" s="5"/>
+      <c r="Z34" s="5"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
-      <c r="Z35" s="4"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+      <c r="W35" s="5"/>
+      <c r="X35" s="5"/>
+      <c r="Y35" s="5"/>
+      <c r="Z35" s="5"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+      <c r="W36" s="5"/>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5"/>
+      <c r="Z36" s="5"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>20</v>
@@ -1916,202 +1951,202 @@
       <c r="D37" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E37" s="4"/>
+      <c r="E37" s="5"/>
       <c r="F37" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="4"/>
-      <c r="W37" s="4"/>
-      <c r="X37" s="4"/>
-      <c r="Y37" s="4"/>
-      <c r="Z37" s="4"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+      <c r="W37" s="5"/>
+      <c r="X37" s="5"/>
+      <c r="Y37" s="5"/>
+      <c r="Z37" s="5"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E38" s="4"/>
+        <v>92</v>
+      </c>
+      <c r="E38" s="5"/>
       <c r="F38" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
-      <c r="Z38" s="4"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+      <c r="W38" s="5"/>
+      <c r="X38" s="5"/>
+      <c r="Y38" s="5"/>
+      <c r="Z38" s="5"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="4"/>
-      <c r="W39" s="4"/>
-      <c r="X39" s="4"/>
-      <c r="Y39" s="4"/>
-      <c r="Z39" s="4"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+      <c r="W39" s="5"/>
+      <c r="X39" s="5"/>
+      <c r="Y39" s="5"/>
+      <c r="Z39" s="5"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="4"/>
-      <c r="W40" s="4"/>
-      <c r="X40" s="4"/>
-      <c r="Y40" s="4"/>
-      <c r="Z40" s="4"/>
+        <v>97</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="5"/>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+      <c r="W40" s="5"/>
+      <c r="X40" s="5"/>
+      <c r="Y40" s="5"/>
+      <c r="Z40" s="5"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
-      <c r="W41" s="4"/>
-      <c r="X41" s="4"/>
-      <c r="Y41" s="4"/>
-      <c r="Z41" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="5"/>
+      <c r="U41" s="5"/>
+      <c r="V41" s="5"/>
+      <c r="W41" s="5"/>
+      <c r="X41" s="5"/>
+      <c r="Y41" s="5"/>
+      <c r="Z41" s="5"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="4"/>
+      <c r="D42" s="5"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="4"/>
+      <c r="G42" s="5"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
-      <c r="W42" s="4"/>
-      <c r="X42" s="4"/>
-      <c r="Y42" s="4"/>
-      <c r="Z42" s="4"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="5"/>
+      <c r="U42" s="5"/>
+      <c r="V42" s="5"/>
+      <c r="W42" s="5"/>
+      <c r="X42" s="5"/>
+      <c r="Y42" s="5"/>
+      <c r="Z42" s="5"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2"/>
@@ -8459,70 +8494,67 @@
     <pageSetUpPr/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
-  </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>98</v>
+      <c r="C2" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>101</v>
+      <c r="B3" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1"/>
@@ -9543,22 +9575,22 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -9583,23 +9615,23 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="6">
+        <v>112</v>
+      </c>
+      <c r="C2" s="7">
         <f>NOW()</f>
-        <v>44869.08592</v>
+        <v>45305.9561</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
